--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20520,6 +20520,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B877" t="n">
+        <v>0</v>
+      </c>
+      <c r="C877" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D877" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E877" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F877" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G877" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20543,6 +20543,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B878" t="n">
+        <v>0</v>
+      </c>
+      <c r="C878" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D878" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E878" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F878" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G878" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20566,6 +20566,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="879">
+      <c r="A879" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B879" t="n">
+        <v>0</v>
+      </c>
+      <c r="C879" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D879" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E879" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F879" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G879" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20589,6 +20589,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="880">
+      <c r="A880" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B880" t="n">
+        <v>0</v>
+      </c>
+      <c r="C880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G880" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20453,7 +20453,7 @@
     </row>
     <row r="874">
       <c r="A874" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B874" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B875" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
     </row>
     <row r="876">
       <c r="A876" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B876" t="n">
         <v>0</v>
@@ -20522,7 +20522,7 @@
     </row>
     <row r="877">
       <c r="A877" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B877" t="n">
         <v>0</v>
@@ -20545,7 +20545,7 @@
     </row>
     <row r="878">
       <c r="A878" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B878" t="n">
         <v>0</v>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="879">
       <c r="A879" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B879" t="n">
         <v>0</v>
@@ -20591,24 +20591,47 @@
     </row>
     <row r="880">
       <c r="A880" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B880" t="n">
+        <v>0</v>
+      </c>
+      <c r="C880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F880" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G880" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B880" t="n">
-        <v>0</v>
-      </c>
-      <c r="C880" t="n">
-        <v>2.33999991416931</v>
-      </c>
-      <c r="D880" t="n">
-        <v>2.33999991416931</v>
-      </c>
-      <c r="E880" t="n">
-        <v>2.33999991416931</v>
-      </c>
-      <c r="F880" t="n">
-        <v>2.33999991416931</v>
-      </c>
-      <c r="G880" t="s">
+      <c r="B881" t="n">
+        <v>0</v>
+      </c>
+      <c r="C881" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D881" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E881" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F881" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G881" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20635,6 +20635,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="882">
+      <c r="A882" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B882" t="n">
+        <v>0</v>
+      </c>
+      <c r="C882" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D882" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E882" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F882" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G882" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B883" t="n">
+        <v>0</v>
+      </c>
+      <c r="C883" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D883" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E883" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F883" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G883" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20681,6 +20681,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="884">
+      <c r="A884" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B884" t="n">
+        <v>0</v>
+      </c>
+      <c r="C884" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D884" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E884" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F884" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G884" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20704,6 +20704,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="885">
+      <c r="A885" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B885" t="n">
+        <v>0</v>
+      </c>
+      <c r="C885" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D885" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E885" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F885" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G885" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20727,6 +20727,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="886">
+      <c r="A886" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B886" t="n">
+        <v>0</v>
+      </c>
+      <c r="C886" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D886" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E886" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F886" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G886" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20750,6 +20750,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="887">
+      <c r="A887" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B887" t="n">
+        <v>0</v>
+      </c>
+      <c r="C887" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D887" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E887" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F887" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G887" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20773,6 +20773,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="888">
+      <c r="A888" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B888" t="n">
+        <v>0</v>
+      </c>
+      <c r="C888" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D888" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E888" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F888" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G888" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20796,6 +20796,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="889">
+      <c r="A889" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B889" t="n">
+        <v>0</v>
+      </c>
+      <c r="C889" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D889" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E889" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F889" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G889" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20819,6 +20819,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B890" t="n">
+        <v>0</v>
+      </c>
+      <c r="C890" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D890" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E890" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F890" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G890" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20842,6 +20842,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="891">
+      <c r="A891" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B891" t="n">
+        <v>0</v>
+      </c>
+      <c r="C891" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D891" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E891" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F891" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G891" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B892" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C892" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D892" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E892" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F892"/>
+      <c r="G892" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20873,15 +20873,17 @@
         <v>5000</v>
       </c>
       <c r="C892" t="n">
-        <v>2.33999991416931</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="D892" t="n">
-        <v>2.33999991416931</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="E892" t="n">
-        <v>2.33999991416931</v>
-      </c>
-      <c r="F892"/>
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F892" t="n">
+        <v>2.25999999046326</v>
+      </c>
       <c r="G892" t="s">
         <v>7</v>
       </c>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20888,6 +20888,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="893">
+      <c r="A893" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B893" t="n">
+        <v>0</v>
+      </c>
+      <c r="C893" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D893" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E893" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F893" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G893" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20911,6 +20911,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="894">
+      <c r="A894" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B894" t="n">
+        <v>0</v>
+      </c>
+      <c r="C894" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D894" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E894" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F894" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G894" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20934,6 +20934,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B895" t="n">
+        <v>0</v>
+      </c>
+      <c r="C895" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D895" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E895" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F895" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G895" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20957,6 +20957,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="896">
+      <c r="A896" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B896" t="n">
+        <v>0</v>
+      </c>
+      <c r="C896" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D896" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E896" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F896" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G896" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -20980,6 +20980,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="897">
+      <c r="A897" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B897" t="n">
+        <v>0</v>
+      </c>
+      <c r="C897" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D897" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E897" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F897" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G897" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -21026,6 +21026,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="899">
+      <c r="A899" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B899" t="n">
+        <v>0</v>
+      </c>
+      <c r="C899" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D899" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E899" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F899" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G899" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -21049,6 +21049,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="900">
+      <c r="A900" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B900" t="n">
+        <v>0</v>
+      </c>
+      <c r="C900" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D900" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E900" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F900" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G900" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -21072,6 +21072,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B901" t="n">
+        <v>0</v>
+      </c>
+      <c r="C901" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D901" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E901" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F901" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G901" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -21095,6 +21095,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="902">
+      <c r="A902" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B902" t="n">
+        <v>0</v>
+      </c>
+      <c r="C902" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D902" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E902" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F902" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G902" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26565,6 +26565,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" t="s">
+        <v>9</v>
+      </c>
+      <c r="B904" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C904" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D904" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E904" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F904" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G904" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26594,6 +26594,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="905">
+      <c r="A905" t="s">
+        <v>9</v>
+      </c>
+      <c r="B905" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C905" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D905" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E905" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F905" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G905" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H905" t="n">
+        <v>0</v>
+      </c>
+      <c r="I905" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26623,6 +26623,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="906">
+      <c r="A906" t="s">
+        <v>9</v>
+      </c>
+      <c r="B906" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C906" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D906" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E906" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F906" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G906" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H906" t="n">
+        <v>0</v>
+      </c>
+      <c r="I906" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26652,6 +26652,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="907">
+      <c r="A907" t="s">
+        <v>9</v>
+      </c>
+      <c r="B907" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C907" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D907" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E907" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F907" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G907" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H907" t="n">
+        <v>0</v>
+      </c>
+      <c r="I907" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26681,6 +26681,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" t="s">
+        <v>9</v>
+      </c>
+      <c r="B908" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C908" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D908" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E908" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F908" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G908" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H908" t="n">
+        <v>0</v>
+      </c>
+      <c r="I908" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26710,6 +26710,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" t="s">
+        <v>9</v>
+      </c>
+      <c r="B909" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C909" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D909" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E909" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F909" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G909" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H909" t="n">
+        <v>0</v>
+      </c>
+      <c r="I909" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26739,6 +26739,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" t="s">
+        <v>9</v>
+      </c>
+      <c r="B910" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C910" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D910" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E910" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F910" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G910" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H910" t="n">
+        <v>0</v>
+      </c>
+      <c r="I910" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26768,6 +26768,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" t="s">
+        <v>9</v>
+      </c>
+      <c r="B911" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C911" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D911" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E911" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F911" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G911" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H911" t="n">
+        <v>0</v>
+      </c>
+      <c r="I911" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CUBE.MI.xlsx
+++ b/data/CUBE.MI.xlsx
@@ -26797,6 +26797,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" t="s">
+        <v>9</v>
+      </c>
+      <c r="B912" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C912" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D912" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E912" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F912" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G912" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H912" t="n">
+        <v>0</v>
+      </c>
+      <c r="I912" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
